--- a/upload/acordos_cooperacao_tecnica.xlsx
+++ b/upload/acordos_cooperacao_tecnica.xlsx
@@ -9,20 +9,20 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11100"/>
   </bookViews>
   <sheets>
     <sheet name="acordos_cooperacao_tecnica" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">acordos_cooperacao_tecnica!$A$1:$K$1873</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">acordos_cooperacao_tecnica!$A$1:$K$1874</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11893" uniqueCount="5465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11901" uniqueCount="5467">
   <si>
     <t>ano</t>
   </si>
@@ -16701,6 +16701,12 @@
   </si>
   <si>
     <t>ASSOCIAÇÃO DE ENSINO DE RIBEIRÃO PRETO</t>
+  </si>
+  <si>
+    <t>O presente Acordo de Cooperação Técnica tem por objeto estabelecer a cooperação mútua entre os partícipes, visando sistematizar o intercâmbio de informações, sem ônus, em caráter personalíssimo e intransferível, por meio da cessão do uso de software do Sistema da Lei Geral de Proteção de Dados Pessoais (LGPD) da Escola de Saúde Pública do Estado de Minas Gerais (ESP-MG) para a EMATER/MG</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/9cEHNCcJXyyGfj2</t>
   </si>
 </sst>
 </file>
@@ -17818,7 +17824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K1873"/>
+  <dimension ref="A1:K1874"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -20790,7 +20796,7 @@
         <v>5122</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>2022</v>
       </c>
@@ -34617,7 +34623,7 @@
         <v>3825</v>
       </c>
     </row>
-    <row r="523" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A523" s="12">
         <v>2021</v>
       </c>
@@ -35283,7 +35289,7 @@
         <v>46266</v>
       </c>
       <c r="I543" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J543" s="3" t="s">
         <v>2215</v>
@@ -35315,7 +35321,7 @@
         <v>46266</v>
       </c>
       <c r="I544" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J544" s="3" t="s">
         <v>2216</v>
@@ -35347,7 +35353,7 @@
         <v>46266</v>
       </c>
       <c r="I545" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J545" s="3" t="s">
         <v>2218</v>
@@ -35379,7 +35385,7 @@
         <v>46266</v>
       </c>
       <c r="I546" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J546" s="3" t="s">
         <v>2219</v>
@@ -35411,7 +35417,7 @@
         <v>46266</v>
       </c>
       <c r="I547" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J547" s="3" t="s">
         <v>2230</v>
@@ -35443,7 +35449,7 @@
         <v>46267</v>
       </c>
       <c r="I548" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J548" t="s">
         <v>3181</v>
@@ -35475,7 +35481,7 @@
         <v>46268</v>
       </c>
       <c r="I549" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J549" t="s">
         <v>3435</v>
@@ -35506,8 +35512,8 @@
       <c r="H550" s="13">
         <v>46273</v>
       </c>
-      <c r="I550" s="12" t="s">
-        <v>14</v>
+      <c r="I550" t="s">
+        <v>110</v>
       </c>
       <c r="J550" s="12" t="s">
         <v>4583</v>
@@ -35539,7 +35545,7 @@
         <v>46274</v>
       </c>
       <c r="I551" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J551" s="7" t="s">
         <v>2618</v>
@@ -35571,7 +35577,7 @@
         <v>46274</v>
       </c>
       <c r="I552" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J552" t="s">
         <v>936</v>
@@ -35603,7 +35609,7 @@
         <v>46275</v>
       </c>
       <c r="I553" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J553" s="3" t="s">
         <v>1924</v>
@@ -35635,7 +35641,7 @@
         <v>46275</v>
       </c>
       <c r="I554" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J554" t="s">
         <v>4899</v>
@@ -35667,7 +35673,7 @@
         <v>46280</v>
       </c>
       <c r="I555" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J555" t="s">
         <v>5057</v>
@@ -35699,7 +35705,7 @@
         <v>46281</v>
       </c>
       <c r="I556" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J556" t="s">
         <v>5113</v>
@@ -35731,7 +35737,7 @@
         <v>2027</v>
       </c>
       <c r="I557" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J557" t="s">
         <v>355</v>
@@ -35763,7 +35769,7 @@
         <v>46282</v>
       </c>
       <c r="I558" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J558" t="s">
         <v>5395</v>
@@ -35795,7 +35801,7 @@
         <v>46284</v>
       </c>
       <c r="I559" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J559" t="s">
         <v>1407</v>
@@ -35827,7 +35833,7 @@
         <v>46285</v>
       </c>
       <c r="I560" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J560" t="s">
         <v>5021</v>
@@ -35859,7 +35865,7 @@
         <v>46288</v>
       </c>
       <c r="I561" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J561" s="3" t="s">
         <v>2383</v>
@@ -35891,7 +35897,7 @@
         <v>46291</v>
       </c>
       <c r="I562" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J562" t="s">
         <v>5388</v>
@@ -35923,7 +35929,7 @@
         <v>46293</v>
       </c>
       <c r="I563" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J563" s="3" t="s">
         <v>2383</v>
@@ -35955,7 +35961,7 @@
         <v>46294</v>
       </c>
       <c r="I564" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J564" t="s">
         <v>4404</v>
@@ -35987,7 +35993,7 @@
         <v>46295</v>
       </c>
       <c r="I565" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J565" s="7" t="s">
         <v>2635</v>
@@ -77925,8 +77931,40 @@
         <v>2637</v>
       </c>
     </row>
+    <row r="1874" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1874">
+        <v>2026</v>
+      </c>
+      <c r="B1874" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1874" t="s">
+        <v>2559</v>
+      </c>
+      <c r="D1874" t="s">
+        <v>3501</v>
+      </c>
+      <c r="E1874" t="s">
+        <v>1909</v>
+      </c>
+      <c r="F1874" t="s">
+        <v>5465</v>
+      </c>
+      <c r="G1874" s="1">
+        <v>44550</v>
+      </c>
+      <c r="H1874" s="1" t="s">
+        <v>2294</v>
+      </c>
+      <c r="I1874" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1874" t="s">
+        <v>5466</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K1873">
+  <autoFilter ref="A1:K1874">
     <sortState ref="A2:K1873">
       <sortCondition ref="H1:H1873"/>
     </sortState>
